--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F642"/>
+  <dimension ref="A1:F646"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18408,6 +18408,118 @@
         <v>-0.03</v>
       </c>
     </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E643" t="n">
+        <v>41000</v>
+      </c>
+      <c r="F643" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E644" t="n">
+        <v>35000</v>
+      </c>
+      <c r="F644" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E645" t="n">
+        <v>-191000</v>
+      </c>
+      <c r="F645" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E646" t="n">
+        <v>-215000</v>
+      </c>
+      <c r="F646" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F646"/>
+  <dimension ref="A1:F648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18520,6 +18520,62 @@
         <v>-0.11</v>
       </c>
     </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E647" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="F647" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E648" t="n">
+        <v>-158000</v>
+      </c>
+      <c r="F648" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F648"/>
+  <dimension ref="A1:F653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18576,6 +18576,146 @@
         <v>-0.19</v>
       </c>
     </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E649" t="n">
+        <v>1015000</v>
+      </c>
+      <c r="F649" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E650" t="n">
+        <v>320000</v>
+      </c>
+      <c r="F650" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E651" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F651" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E652" t="n">
+        <v>-360000</v>
+      </c>
+      <c r="F652" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E653" t="n">
+        <v>-152000</v>
+      </c>
+      <c r="F653" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F653"/>
+  <dimension ref="A1:F658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18716,6 +18716,146 @@
         <v>-0.06</v>
       </c>
     </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E654" t="n">
+        <v>148000</v>
+      </c>
+      <c r="F654" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E655" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="F655" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E656" t="n">
+        <v>-316000</v>
+      </c>
+      <c r="F656" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E657" t="n">
+        <v>-389000</v>
+      </c>
+      <c r="F657" t="n">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E658" t="n">
+        <v>-205000</v>
+      </c>
+      <c r="F658" t="n">
+        <v>-0.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F658"/>
+  <dimension ref="A1:F667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18856,6 +18856,258 @@
         <v>-0.08</v>
       </c>
     </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E659" t="n">
+        <v>180000</v>
+      </c>
+      <c r="F659" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E660" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F660" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E661" t="n">
+        <v>129000</v>
+      </c>
+      <c r="F661" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E662" t="n">
+        <v>831000</v>
+      </c>
+      <c r="F662" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E663" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F663" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E664" t="n">
+        <v>-1446000</v>
+      </c>
+      <c r="F664" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E665" t="n">
+        <v>-337000</v>
+      </c>
+      <c r="F665" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E666" t="n">
+        <v>-46000</v>
+      </c>
+      <c r="F666" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E667" t="n">
+        <v>-74000</v>
+      </c>
+      <c r="F667" t="n">
+        <v>-0.18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F667"/>
+  <dimension ref="A1:F672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19108,6 +19108,146 @@
         <v>-0.18</v>
       </c>
     </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E668" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F668" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E669" t="n">
+        <v>240000</v>
+      </c>
+      <c r="F669" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E670" t="n">
+        <v>-1345000</v>
+      </c>
+      <c r="F670" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E671" t="n">
+        <v>-144000</v>
+      </c>
+      <c r="F671" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E672" t="n">
+        <v>-444000</v>
+      </c>
+      <c r="F672" t="n">
+        <v>-0.38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F672"/>
+  <dimension ref="A1:F702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19248,6 +19248,846 @@
         <v>-0.38</v>
       </c>
     </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E673" t="n">
+        <v>-2000000</v>
+      </c>
+      <c r="F673" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E674" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="F674" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E675" t="n">
+        <v>-350000</v>
+      </c>
+      <c r="F675" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E676" t="n">
+        <v>-400000</v>
+      </c>
+      <c r="F676" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E677" t="n">
+        <v>-200000</v>
+      </c>
+      <c r="F677" t="n">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E678" t="n">
+        <v>-29000</v>
+      </c>
+      <c r="F678" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E679" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="F679" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E680" t="n">
+        <v>-200000</v>
+      </c>
+      <c r="F680" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E681" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="F681" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E682" t="n">
+        <v>-60000</v>
+      </c>
+      <c r="F682" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E683" t="n">
+        <v>-200000</v>
+      </c>
+      <c r="F683" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E684" t="n">
+        <v>-200000</v>
+      </c>
+      <c r="F684" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E685" t="n">
+        <v>-25000</v>
+      </c>
+      <c r="F685" t="n">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E686" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="F686" t="n">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E687" t="n">
+        <v>-67000</v>
+      </c>
+      <c r="F687" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E688" t="n">
+        <v>-1500000</v>
+      </c>
+      <c r="F688" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E689" t="n">
+        <v>-60000</v>
+      </c>
+      <c r="F689" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E690" t="n">
+        <v>-39000</v>
+      </c>
+      <c r="F690" t="n">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>6191</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>精成科</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E691" t="n">
+        <v>-67000</v>
+      </c>
+      <c r="F691" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E692" t="n">
+        <v>-45000</v>
+      </c>
+      <c r="F692" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>6271</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>同欣電</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E693" t="n">
+        <v>-37000</v>
+      </c>
+      <c r="F693" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E694" t="n">
+        <v>-50000</v>
+      </c>
+      <c r="F694" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>6278</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E695" t="n">
+        <v>-55000</v>
+      </c>
+      <c r="F695" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E696" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="F696" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E697" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="F697" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E698" t="n">
+        <v>-265000</v>
+      </c>
+      <c r="F698" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E699" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="F699" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E700" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="F700" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E701" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="F701" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E702" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="F702" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F702"/>
+  <dimension ref="A1:F709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20088,6 +20088,202 @@
         <v>0</v>
       </c>
     </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E703" t="n">
+        <v>69000</v>
+      </c>
+      <c r="F703" t="n">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E704" t="n">
+        <v>388000</v>
+      </c>
+      <c r="F704" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E705" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F705" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E706" t="n">
+        <v>265000</v>
+      </c>
+      <c r="F706" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E707" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="F707" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>6278</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E708" t="n">
+        <v>-519000</v>
+      </c>
+      <c r="F708" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E709" t="n">
+        <v>-61000</v>
+      </c>
+      <c r="F709" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F709"/>
+  <dimension ref="A1:F711"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20284,6 +20284,62 @@
         <v>0.01</v>
       </c>
     </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E710" t="n">
+        <v>461000</v>
+      </c>
+      <c r="F710" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E711" t="n">
+        <v>-440000</v>
+      </c>
+      <c r="F711" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F711"/>
+  <dimension ref="A1:F713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20340,6 +20340,62 @@
         <v>-0.05</v>
       </c>
     </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E712" t="n">
+        <v>-150000</v>
+      </c>
+      <c r="F712" t="n">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E713" t="n">
+        <v>-95000</v>
+      </c>
+      <c r="F713" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F713"/>
+  <dimension ref="A1:F716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20396,6 +20396,90 @@
         <v>-0.03</v>
       </c>
     </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E714" t="n">
+        <v>-2250000</v>
+      </c>
+      <c r="F714" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E715" t="n">
+        <v>-347000</v>
+      </c>
+      <c r="F715" t="n">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E716" t="n">
+        <v>-95000</v>
+      </c>
+      <c r="F716" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F716"/>
+  <dimension ref="A1:F723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20480,6 +20480,202 @@
         <v>-0.03</v>
       </c>
     </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E717" t="n">
+        <v>173000</v>
+      </c>
+      <c r="F717" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E718" t="n">
+        <v>-2500000</v>
+      </c>
+      <c r="F718" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E719" t="n">
+        <v>-4284000</v>
+      </c>
+      <c r="F719" t="n">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E720" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="F720" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>6278</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E721" t="n">
+        <v>-2226000</v>
+      </c>
+      <c r="F721" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E722" t="n">
+        <v>-469000</v>
+      </c>
+      <c r="F722" t="n">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E723" t="n">
+        <v>-266000</v>
+      </c>
+      <c r="F723" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F723"/>
+  <dimension ref="A1:F736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20676,6 +20676,370 @@
         <v>-0.07000000000000001</v>
       </c>
     </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E724" t="n">
+        <v>681000</v>
+      </c>
+      <c r="F724" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E725" t="n">
+        <v>132000</v>
+      </c>
+      <c r="F725" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E726" t="n">
+        <v>316000</v>
+      </c>
+      <c r="F726" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E727" t="n">
+        <v>-5000000</v>
+      </c>
+      <c r="F727" t="n">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E728" t="n">
+        <v>-1238000</v>
+      </c>
+      <c r="F728" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E729" t="n">
+        <v>-800000</v>
+      </c>
+      <c r="F729" t="n">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E730" t="n">
+        <v>-697000</v>
+      </c>
+      <c r="F730" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E731" t="n">
+        <v>-471000</v>
+      </c>
+      <c r="F731" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E732" t="n">
+        <v>-3482000</v>
+      </c>
+      <c r="F732" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E733" t="n">
+        <v>-11000</v>
+      </c>
+      <c r="F733" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>6278</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E734" t="n">
+        <v>-447000</v>
+      </c>
+      <c r="F734" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E735" t="n">
+        <v>-512000</v>
+      </c>
+      <c r="F735" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E736" t="n">
+        <v>-205000</v>
+      </c>
+      <c r="F736" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F736"/>
+  <dimension ref="A1:F739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21040,6 +21040,90 @@
         <v>-0.06</v>
       </c>
     </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E737" t="n">
+        <v>256000</v>
+      </c>
+      <c r="F737" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E738" t="n">
+        <v>96000</v>
+      </c>
+      <c r="F738" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E739" t="n">
+        <v>-366000</v>
+      </c>
+      <c r="F739" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F739"/>
+  <dimension ref="A1:F745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21124,6 +21124,174 @@
         <v>-0.26</v>
       </c>
     </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E740" t="n">
+        <v>360000</v>
+      </c>
+      <c r="F740" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E741" t="n">
+        <v>321000</v>
+      </c>
+      <c r="F741" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E742" t="n">
+        <v>68000</v>
+      </c>
+      <c r="F742" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E743" t="n">
+        <v>-4482000</v>
+      </c>
+      <c r="F743" t="n">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E744" t="n">
+        <v>-579000</v>
+      </c>
+      <c r="F744" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E745" t="n">
+        <v>-928000</v>
+      </c>
+      <c r="F745" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F745"/>
+  <dimension ref="A1:F751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21292,6 +21292,174 @@
         <v>-0.19</v>
       </c>
     </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E746" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F746" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E747" t="n">
+        <v>304000</v>
+      </c>
+      <c r="F747" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E748" t="n">
+        <v>169000</v>
+      </c>
+      <c r="F748" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E749" t="n">
+        <v>-4313000</v>
+      </c>
+      <c r="F749" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E750" t="n">
+        <v>-152000</v>
+      </c>
+      <c r="F750" t="n">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E751" t="n">
+        <v>-193000</v>
+      </c>
+      <c r="F751" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F751"/>
+  <dimension ref="A1:F756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21460,6 +21460,146 @@
         <v>-0.17</v>
       </c>
     </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E752" t="n">
+        <v>364000</v>
+      </c>
+      <c r="F752" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E753" t="n">
+        <v>85000</v>
+      </c>
+      <c r="F753" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E754" t="n">
+        <v>76000</v>
+      </c>
+      <c r="F754" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E755" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F755" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E756" t="n">
+        <v>-322000</v>
+      </c>
+      <c r="F756" t="n">
+        <v>-1.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F756"/>
+  <dimension ref="A1:F764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21600,6 +21600,230 @@
         <v>-1.28</v>
       </c>
     </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E757" t="n">
+        <v>1682000</v>
+      </c>
+      <c r="F757" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E758" t="n">
+        <v>1256000</v>
+      </c>
+      <c r="F758" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E759" t="n">
+        <v>67000</v>
+      </c>
+      <c r="F759" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>4979</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>華星光</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E760" t="n">
+        <v>956000</v>
+      </c>
+      <c r="F760" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E761" t="n">
+        <v>29000</v>
+      </c>
+      <c r="F761" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E762" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F762" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E763" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F763" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E764" t="n">
+        <v>-1034000</v>
+      </c>
+      <c r="F764" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F764"/>
+  <dimension ref="A1:F767"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21824,6 +21824,90 @@
         <v>-0.92</v>
       </c>
     </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E765" t="n">
+        <v>385000</v>
+      </c>
+      <c r="F765" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E766" t="n">
+        <v>217000</v>
+      </c>
+      <c r="F766" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E767" t="n">
+        <v>199000</v>
+      </c>
+      <c r="F767" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F767"/>
+  <dimension ref="A1:F777"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21908,6 +21908,286 @@
         <v>0.12</v>
       </c>
     </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E768" t="n">
+        <v>118000</v>
+      </c>
+      <c r="F768" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E769" t="n">
+        <v>892000</v>
+      </c>
+      <c r="F769" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E770" t="n">
+        <v>57000</v>
+      </c>
+      <c r="F770" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E771" t="n">
+        <v>156000</v>
+      </c>
+      <c r="F771" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E772" t="n">
+        <v>448000</v>
+      </c>
+      <c r="F772" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E773" t="n">
+        <v>600000</v>
+      </c>
+      <c r="F773" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E774" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F774" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E775" t="n">
+        <v>178000</v>
+      </c>
+      <c r="F775" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E776" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F776" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E777" t="n">
+        <v>285000</v>
+      </c>
+      <c r="F777" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F777"/>
+  <dimension ref="A1:F786"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22188,6 +22188,258 @@
         <v>0.17</v>
       </c>
     </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E778" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F778" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E779" t="n">
+        <v>204000</v>
+      </c>
+      <c r="F779" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E780" t="n">
+        <v>199000</v>
+      </c>
+      <c r="F780" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E781" t="n">
+        <v>1008000</v>
+      </c>
+      <c r="F781" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E782" t="n">
+        <v>113000</v>
+      </c>
+      <c r="F782" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E783" t="n">
+        <v>800000</v>
+      </c>
+      <c r="F783" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E784" t="n">
+        <v>101000</v>
+      </c>
+      <c r="F784" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E785" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F785" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>20261019</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>8358</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>金居</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E786" t="n">
+        <v>653000</v>
+      </c>
+      <c r="F786" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F786"/>
+  <dimension ref="A1:F792"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22440,6 +22440,174 @@
         <v>0.11</v>
       </c>
     </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="E787" t="n">
+        <v>4703000</v>
+      </c>
+      <c r="F787" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E788" t="n">
+        <v>279000</v>
+      </c>
+      <c r="F788" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E789" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="F789" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E790" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F790" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E791" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F791" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E792" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F792" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F792"/>
+  <dimension ref="A1:F799"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22608,6 +22608,202 @@
         <v>0.05</v>
       </c>
     </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E793" t="n">
+        <v>67000</v>
+      </c>
+      <c r="F793" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E794" t="n">
+        <v>236000</v>
+      </c>
+      <c r="F794" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E795" t="n">
+        <v>114000</v>
+      </c>
+      <c r="F795" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E796" t="n">
+        <v>190000</v>
+      </c>
+      <c r="F796" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E797" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="F797" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E798" t="n">
+        <v>2170000</v>
+      </c>
+      <c r="F798" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E799" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F799" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F799"/>
+  <dimension ref="A1:F801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22804,6 +22804,62 @@
         <v>0.1</v>
       </c>
     </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E800" t="n">
+        <v>547000</v>
+      </c>
+      <c r="F800" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>20261022</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>4966</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>譜瑞-KY</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="E801" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="F801" t="n">
+        <v>-0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F801"/>
+  <dimension ref="A1:F810"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22857,7 +22857,259 @@
         <v>-1000</v>
       </c>
       <c r="F801" t="n">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>20261027</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E802" t="n">
+        <v>375000</v>
+      </c>
+      <c r="F802" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>20261027</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E803" t="n">
+        <v>80000</v>
+      </c>
+      <c r="F803" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>20261027</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E804" t="n">
+        <v>969000</v>
+      </c>
+      <c r="F804" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>20261027</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E805" t="n">
+        <v>90000</v>
+      </c>
+      <c r="F805" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>20261027</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E806" t="n">
+        <v>80000</v>
+      </c>
+      <c r="F806" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>20261027</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E807" t="n">
+        <v>1073000</v>
+      </c>
+      <c r="F807" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>20261027</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E808" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F808" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>20261027</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E809" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="F809" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>20261027</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E810" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="F810" t="n">
+        <v>-0.03</v>
       </c>
     </row>
   </sheetData>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F810"/>
+  <dimension ref="A1:F819"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23112,6 +23112,258 @@
         <v>-0.03</v>
       </c>
     </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>20261028</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E811" t="n">
+        <v>657000</v>
+      </c>
+      <c r="F811" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>20261028</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E812" t="n">
+        <v>73000</v>
+      </c>
+      <c r="F812" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>20261028</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E813" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F813" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>20261028</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E814" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F814" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>20261028</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E815" t="n">
+        <v>1976000</v>
+      </c>
+      <c r="F815" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>20261028</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E816" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F816" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>20261028</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E817" t="n">
+        <v>157000</v>
+      </c>
+      <c r="F817" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>20261028</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E818" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="F818" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>20261028</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E819" t="n">
+        <v>-76000</v>
+      </c>
+      <c r="F819" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F819"/>
+  <dimension ref="A1:F825"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23364,6 +23364,174 @@
         <v>-0.03</v>
       </c>
     </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>20261029</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E820" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F820" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>20261029</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E821" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F821" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>20261029</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E822" t="n">
+        <v>38000</v>
+      </c>
+      <c r="F822" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>20261029</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E823" t="n">
+        <v>80000</v>
+      </c>
+      <c r="F823" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>20261029</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E824" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F824" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>20261029</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>減少</t>
+        </is>
+      </c>
+      <c r="E825" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="F825" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日異動紀錄.xlsx
+++ b/每日異動紀錄.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F825"/>
+  <dimension ref="A1:F830"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23532,6 +23532,146 @@
         <v>-0.02</v>
       </c>
     </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>20261030</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E826" t="n">
+        <v>205000</v>
+      </c>
+      <c r="F826" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>20261030</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E827" t="n">
+        <v>61000</v>
+      </c>
+      <c r="F827" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>20261030</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E828" t="n">
+        <v>79000</v>
+      </c>
+      <c r="F828" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>20261030</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E829" t="n">
+        <v>1644000</v>
+      </c>
+      <c r="F829" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>20261030</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>增加</t>
+        </is>
+      </c>
+      <c r="E830" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F830" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
